--- a/data/trans_camb/LAWTONB_2R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,64</t>
+          <t>-1,37; 8,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,96</t>
+          <t>-3,59; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,16</t>
+          <t>-3,29; 3,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 6,03</t>
+          <t>-3,26; 5,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,94</t>
+          <t>-4,46; 3,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 0,82</t>
+          <t>-3,74; 3,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,56</t>
+          <t>-1,07; 5,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,67</t>
+          <t>-2,82; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,53</t>
+          <t>-2,54; 2,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,06%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 172,02</t>
+          <t>-18,36; 171,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 92,66</t>
+          <t>-46,57; 90,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 98,33</t>
+          <t>-37,4; 91,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 77,7</t>
+          <t>-27,03; 74,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 54,36</t>
+          <t>-36,78; 50,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 9,59</t>
+          <t>-29,58; 48,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 77,68</t>
+          <t>-12,53; 79,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,87; 38,95</t>
+          <t>-30,5; 49,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,7; 19,97</t>
+          <t>-24,91; 41,25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,64</t>
+          <t>18,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>13,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 21,05</t>
+          <t>4,77; 21,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,97</t>
+          <t>-2,82; 11,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 13,9</t>
+          <t>-1,3; 12,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 19,44</t>
+          <t>5,48; 19,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 17,23</t>
+          <t>2,02; 16,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 24,36</t>
+          <t>12,13; 24,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 17,5</t>
+          <t>6,67; 18,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 12,8</t>
+          <t>1,61; 13,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,37</t>
+          <t>8,57; 18,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,82; 120,22</t>
+          <t>15,3; 118,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 66,96</t>
+          <t>-11,52; 63,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 77,2</t>
+          <t>-5,3; 67,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,04; 81,17</t>
+          <t>16,47; 86,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 70,1</t>
+          <t>6,31; 68,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,41; 106,38</t>
+          <t>38,15; 107,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,12; 79,39</t>
+          <t>24,83; 85,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 56,93</t>
+          <t>6,15; 58,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,08; 81,23</t>
+          <t>28,92; 82,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,12</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>9,84</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>6,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 12,68</t>
+          <t>3,25; 12,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,21</t>
+          <t>-1,55; 6,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,14</t>
+          <t>-0,65; 6,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 12,2</t>
+          <t>3,03; 12,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 9,47</t>
+          <t>0,17; 9,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 11,08</t>
+          <t>6,31; 13,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 11,03</t>
+          <t>4,38; 10,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,65; 6,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,88</t>
+          <t>4,03; 9,77</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,5; 117,73</t>
+          <t>20,35; 112,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 60,9</t>
+          <t>-10,7; 60,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 67,21</t>
+          <t>-3,98; 65,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,41; 74,93</t>
+          <t>14,16; 75,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 59,64</t>
+          <t>0,17; 56,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,78; 62,42</t>
+          <t>30,66; 87,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,45; 76,46</t>
+          <t>24,38; 72,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,94; 46,12</t>
+          <t>3,36; 45,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 51,68</t>
+          <t>22,35; 69,0</t>
         </is>
       </c>
     </row>
